--- a/Result/profitability/5398.xlsx
+++ b/Result/profitability/5398.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.04</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01125</v>
+        <v>0.02375</v>
       </c>
       <c r="N2" t="n">
-        <v>26.14625</v>
+        <v>26.1875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.19</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.01750000000000001</v>
+        <v>0.004999999999999998</v>
       </c>
       <c r="N3" t="n">
-        <v>24.615</v>
+        <v>25.26</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.006250000000000004</v>
+        <v>0.03625</v>
       </c>
       <c r="N4" t="n">
-        <v>23.955</v>
+        <v>29.27125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01375000000000001</v>
+        <v>-0.0425</v>
       </c>
       <c r="N5" t="n">
-        <v>26.6175</v>
+        <v>24.51875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.05500000000000001</v>
+        <v>-0.0525</v>
       </c>
       <c r="N6" t="n">
-        <v>23.1825</v>
+        <v>23.1925</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.04</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.065</v>
+        <v>-0.055</v>
       </c>
       <c r="N7" t="n">
-        <v>23.11625</v>
+        <v>22.85</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.3</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03500000000000001</v>
+        <v>0.009999999999999998</v>
       </c>
       <c r="N8" t="n">
-        <v>22.56</v>
+        <v>26.97625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9846,6 +9846,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>39</v>
+      </c>
+      <c r="D75" t="n">
+        <v>25</v>
+      </c>
+      <c r="E75" t="n">
+        <v>14</v>
+      </c>
+      <c r="F75" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.98%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>7</v>
+      </c>
+      <c r="K75" t="n">
+        <v>7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.03375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.73625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.636363636363636</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>35.33</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>75.17021276595744</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6216216216216216</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-16.79000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3192622171515498</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
